--- a/results/job_matches_2026-10-01.xlsx
+++ b/results/job_matches_2026-10-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>IAM, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Oozie, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ae16726479683f</t>
+          <t>https://www.indeed.com/viewjob?jk=e93507bcf9f653a6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057d3f14e1d878f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ae16726479683f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fa3ea752ece8fd</t>
+          <t>https://www.indeed.com/viewjob?jk=057d3f14e1d878f3</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python/AWS)</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e9bddd262f10a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5eab9d45a7707f9c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -806,12 +806,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a88e47fd9a09b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab75b27388163f6</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -841,19 +841,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1c8cb0925460a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9f207b6755f4c7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,29 +876,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e514f15ff0b1be4b</t>
+          <t>https://www.indeed.com/viewjob?jk=24e9bddd262f10a8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Sr. Automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68101adf03f8ea37</t>
+          <t>https://www.indeed.com/viewjob?jk=cb99ce16f3e25727</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Sr Engineer - FinOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e4c25ad47ec8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8b97a5e70063530e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HSO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala</t>
+          <t>API Gateway, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b97a5e70063530e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4f187ec5e311d0c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSO</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4f187ec5e311d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=99b31bf06061c552</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>DevOps Sr Engineer - FinOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Athena, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b31bf06061c552</t>
+          <t>https://www.indeed.com/viewjob?jk=48e4c25ad47ec8fe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Spring, Kafka, CI/CD, AI tools, Glue, RDS, DynamoDB) (Enterprise Platforms Technology )</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Dataflow, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d57da68f94cf58</t>
+          <t>https://www.indeed.com/viewjob?jk=b53e345da3563756</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Azure Data Engineer Senior</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d44b35a8a09b64</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8b1810e1fdd4c8</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer-6</t>
+          <t>Databricks Architect-4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Photon, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd99fa28f8689eac</t>
+          <t>https://www.indeed.com/viewjob?jk=66f5b68676765609</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Databricks Architect-4</t>
+          <t>Senior Java Full Stack Developer-6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Photon, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f5b68676765609</t>
+          <t>https://www.indeed.com/viewjob?jk=dd99fa28f8689eac</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer – Supply Chain</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e5916ba993e4752</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95a607857d8a63</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Precision Analytical Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McMinnville, OR, US USA</t>
+          <t>Maple Grove, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
+          <t>https://www.indeed.com/viewjob?jk=192ac4a678cf384e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Databricks Engineer - Contract (contract)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95a607857d8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e29091a2e4371e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Enterprise Data- Data Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GBU Life</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Maple Grove, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=192ac4a678cf384e</t>
+          <t>https://www.indeed.com/viewjob?jk=647d32eb31b1193e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Engineer - Contract (contract)</t>
+          <t>Senior Database Developer - C13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e29091a2e4371e</t>
+          <t>https://www.indeed.com/viewjob?jk=75576932f59b7e13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enterprise Data- Data Engineer I</t>
+          <t>Sr. AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GBU Life</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=647d32eb31b1193e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT Data Specialist (US)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Polars, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b73486152212a0fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef70bd0057544fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d01528e1099d2199</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Database Developer - C13</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Adonis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75576932f59b7e13</t>
+          <t>https://www.indeed.com/viewjob?jk=b0454d0d787afaef</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Remote</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98f02f8244206</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>FNBO - First National Bank of Omaha</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
+          <t>https://www.indeed.com/viewjob?jk=9f82e2ce098dec35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Engineer (SQL, AWS, &amp; Java)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Adonis</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0454d0d787afaef</t>
+          <t>https://www.indeed.com/viewjob?jk=93b33418deacae1b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98f02f8244206</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb1f94893c5712e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FNBO - First National Bank of Omaha</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f82e2ce098dec35</t>
+          <t>https://www.indeed.com/viewjob?jk=e0615045d00daaed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SQL, AWS, &amp; Java)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b33418deacae1b</t>
+          <t>https://www.indeed.com/viewjob?jk=897b2194be6b7543</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Vida Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, RDS, GCP, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb1f94893c5712e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f62682570ca4564</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0615045d00daaed</t>
+          <t>https://www.indeed.com/viewjob?jk=a38962dce888067f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dynatrace Platform Engineer</t>
+          <t>Data Engineer / Data Platform Engineer Internship Spring 2027 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RHONDOS</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66919fdddcdfcb04</t>
+          <t>https://www.indeed.com/viewjob?jk=2fea70543399a83d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dynatrace Consultant – Professional Services</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Medallion Architecture, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd30fca3b2ed50b</t>
+          <t>https://www.indeed.com/viewjob?jk=621931178c25b346</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist ADAS Analytics Machine Learning</t>
+          <t>Python Developer-6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, ELT, MLOps, MLflow, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64507608c433c446</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0b13030305a263</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42d956d4515afe7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2965ad3fac6e9b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer ADAS Fleet Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b2194be6b7543</t>
+          <t>https://www.indeed.com/viewjob?jk=11ad6f4a442569a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Software Engineer – SaaS &amp; Data Migration Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>Solen Software Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2267,46 +2267,46 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, Azure, GCP, Scala, SQL Server, DataOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f62682570ca4564</t>
+          <t>https://www.indeed.com/viewjob?jk=1e93b4193751c0db</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Conversational BI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Snowflake, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38962dce888067f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb3b71809e4f10b7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Spring 2027 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fea70543399a83d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Integration Developer/Admin (Senior Application Development Analyst)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Judicial Council of California</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Medallion Architecture, Spark, PySpark, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, MySQL, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621931178c25b346</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d92a3c9beacac9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack .Net Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>O.C. Tanner</t>
+          <t>Starr Companies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb849609aeed9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ce193f64bbb24a65</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Python Developer-6</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0b13030305a263</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac16ebb3b7d3a45</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2965ad3fac6e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d08c7ede9b3f07e5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer ADAS Fleet Analytics</t>
+          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,54 +2526,54 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ad6f4a442569a8</t>
+          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack .Net Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Starr Companies</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce193f64bbb24a65</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8fa8b2a51a2522</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Engineer I, Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac16ebb3b7d3a45</t>
+          <t>https://www.indeed.com/viewjob?jk=995670ae7da973ef</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>BI Developer &amp; Production Support Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Snowflake, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08c7ede9b3f07e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1bbd59742c441b3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Threat &amp; Exposure Management Platform Engineer</t>
+          <t>Enterprise Semantic Layer &amp; Ontology Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, Dimensional Modeling, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d05800edeb9ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=327f8fe14e958d2a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Conversational BI Engineer</t>
+          <t>Data Engineer-Wearables &amp; iOT Analytics (176270)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Snowflake, ELT, Power BI, MLflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3b71809e4f10b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b5d615a2b140cb52</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
+          <t>https://www.indeed.com/viewjob?jk=d62003cb9f83aeb6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1aa4380989d8a52</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Integration Developer/Admin (Senior Application Development Analyst)</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Judicial Council of California</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, MySQL, ETL, Talend, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d92a3c9beacac9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b84f726efca9029</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Site Reliability Engineer- FedRamp</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
+          <t>AWS, RDS, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aaf84515bf65e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c05522799acac5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer I, Data Engineering</t>
+          <t>Senior Site Reliability Infrastructure Engineer- Fedramp</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995670ae7da973ef</t>
+          <t>https://www.indeed.com/viewjob?jk=08d06855bbcf79aa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5, Marketing and Messaging Experimentation</t>
+          <t>Senior Site Reliability Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d91349e906a83d</t>
+          <t>https://www.indeed.com/viewjob?jk=964c0e05d4eca96b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Claude, Node JS, Typescript, Python)</t>
+          <t>Apache Spark Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab3cde603c13024</t>
+          <t>https://www.indeed.com/viewjob?jk=e992d6bfc308d8bb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Technology</t>
+          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hill's Pet Nutrition</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e21b621ca9c3081</t>
+          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Somerset, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbbfb150a6dcd5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c042f7e9d0f0b75</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project-Based) - Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b4726a6ec8ee51c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb19bd4ef6a4ada2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BI Developer &amp; Production Support Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Snowflake, ELT, Power BI, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1bbd59742c441b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a0f122e9187f4e1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterprise Semantic Layer &amp; Ontology Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, Dimensional Modeling, ELT, Power BI, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327f8fe14e958d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d07c3bb23686820</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer-Wearables &amp; iOT Analytics (176270)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5d615a2b140cb52</t>
+          <t>https://www.indeed.com/viewjob?jk=211b0a055f958ee2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>Full-Stack Engineer 5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62003cb9f83aeb6</t>
+          <t>https://www.indeed.com/viewjob?jk=64b2e71c99f69dd6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1aa4380989d8a52</t>
+          <t>https://www.indeed.com/viewjob?jk=0bdd28ae23a357c1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b84f726efca9029</t>
+          <t>https://www.indeed.com/viewjob?jk=2d06a6189a87b46f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer- FedRamp</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c05522799acac5</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc840015b470f1d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Infrastructure Engineer- Fedramp</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d06855bbcf79aa</t>
+          <t>https://www.indeed.com/viewjob?jk=544fd4c8961f1ea1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (FedRAMP)</t>
+          <t>Full-stack Engineer 4, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964c0e05d4eca96b</t>
+          <t>https://www.indeed.com/viewjob?jk=e32202cd85d558d0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e992d6bfc308d8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2c8d56a4de6d75</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hill's Pet Nutrition</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8711133b275b7eb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Application Architect</t>
+          <t>Full-stack Engineer 4 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f83563c96ec7f7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a1054d75a23b6d7e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Python, AWS, Typescript)</t>
+          <t>Full Stack Engineer 4 (Global Payment Network)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b49f39edeab7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb953856e305a64</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9b624ac55b1048d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7b649fedb1b1f4</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abb4feae415dce7</t>
+          <t>https://www.indeed.com/viewjob?jk=f98b7445f4c23e54</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+          <t>Data Platform Engineer I</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa843bcedcc0999</t>
+          <t>https://www.indeed.com/viewjob?jk=c15de344a8583c9e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Threat Intelligence</t>
+          <t>Amazon Connect Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, PostgreSQL, CI/CD, GitHub Actions, Docker, AKS</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Scala, DynamoDB, REST API integration, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3c8c0c1096d1374</t>
+          <t>https://www.indeed.com/viewjob?jk=deaae074113ff24a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI and Software Solutions Architect (Remote, Contract)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>INFUSE</t>
+          <t>foureyes</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfbdeb14e9a28d7</t>
+          <t>https://www.indeed.com/viewjob?jk=129e88ac4f26e5cc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Sr. Software Engineer, Engineering Applications</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad035bddd06542e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f46dbaea5d78f85</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>AI and Software Solutions Architect (Remote, Contract)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>INFUSE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730949159ddc5619</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfbdeb14e9a28d7</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73326af3eb8dfe5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad035bddd06542e8</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df313ae793a47b9</t>
+          <t>https://www.indeed.com/viewjob?jk=730949159ddc5619</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Marketing Management (EMM)</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9a49c01a3e9816</t>
+          <t>https://www.indeed.com/viewjob?jk=c73326af3eb8dfe5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=7df313ae793a47b9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Advisor III, Data &amp; MLOps</t>
+          <t>Programmer I and Programmer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Community College of Baltimore County</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Catonsville, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Power BI, MLOps, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399a462361080234</t>
+          <t>https://www.indeed.com/viewjob?jk=70e78631b1d5b1e5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Enterprise Marketing Management (EMM)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>First Bank</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,262 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d9a49c01a3e9816</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Advisor III, Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Phillips 66</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Power BI, MLOps, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=399a462361080234</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87565d685b23a868</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19069c3d35411178</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9703405ee731b3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Wilmington, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56aea2a70012464c</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=55d0379462176349</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Threat Intelligence</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Proofpoint</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, ECS, RDS, PostgreSQL, CI/CD, GitHub Actions, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3c8c0c1096d1374</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-01.xlsx
+++ b/results/job_matches_2026-10-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer</t>
+          <t>Devops &amp; Data Pipeline Engineer-6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057d3f14e1d878f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8607d279e78ca47a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Devops &amp; Data Pipeline Engineer-6</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RelMap Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8607d279e78ca47a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c20ad72a268b77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior GCP Data Engineer Consultant – BigQuery &amp; Airflow</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RelMap Software</t>
+          <t>Keyhole Software</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, Redshift, S3, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c20ad72a268b77</t>
+          <t>https://www.indeed.com/viewjob?jk=ce929b1244d5c531</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer Consultant – BigQuery &amp; Airflow</t>
+          <t>Business Intelligence Senior Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Keyhole Software</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce929b1244d5c531</t>
+          <t>https://www.indeed.com/viewjob?jk=28d33086583723d4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Business Intelligence Senior Analyst</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>ThinkPoint Solutions Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, MySQL, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d33086583723d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca879c0ea096dbfb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ThinkPoint Solutions Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca879c0ea096dbfb</t>
+          <t>https://www.indeed.com/viewjob?jk=5eab9d45a7707f9c</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eab9d45a7707f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab75b27388163f6</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab75b27388163f6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9f207b6755f4c7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pillsbury Winthrop Shaw Pittman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9f207b6755f4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4506845d5307539</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python/AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e9bddd262f10a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8b97a5e70063530e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer</t>
+          <t>DevOps Sr Engineer - FinOps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Athena, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb99ce16f3e25727</t>
+          <t>https://www.indeed.com/viewjob?jk=48e4c25ad47ec8fe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b97a5e70063530e</t>
+          <t>https://www.indeed.com/viewjob?jk=b53e345da3563756</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSO</t>
+          <t>CMG Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Dataflow, Spark, Scala, Kafka</t>
+          <t>ECS, RDS, Azure, Data Factory, Event Hubs, Kafka, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4f187ec5e311d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=9112581e70dc489f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Azure Data Engineer Senior</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b31bf06061c552</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8b1810e1fdd4c8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Sr Engineer - FinOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>Southern Hobby Distribution</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e4c25ad47ec8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7d102e066fd479ad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CIM GROUP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, PostgreSQL, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53e345da3563756</t>
+          <t>https://www.indeed.com/viewjob?jk=e1dc346effcd7bb8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CMG Financial</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Event Hubs, Kafka, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112581e70dc489f</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc9469609f69082</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Data Engineer Senior</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8b1810e1fdd4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3bff06af76c0e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snr. Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Southern Hobby Distribution</t>
+          <t>KnowBe4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, Azure, GCP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d102e066fd479ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5cb08dca80f82f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Platform Engineer, Cybersecurity Operations</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CIM GROUP</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, PostgreSQL, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dc346effcd7bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed676bd8243856</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3bff06af76c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=dac275bf36488a40</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect - Microsoft Fabric</t>
+          <t>Senior Java Full Stack Developer-6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc9469609f69082</t>
+          <t>https://www.indeed.com/viewjob?jk=dd99fa28f8689eac</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snr. Site Reliability Engineer (Remote)</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KnowBe4</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, Azure, GCP</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5cb08dca80f82f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95a607857d8a63</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Engineer, Cybersecurity Operations</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>FCCI Insurance Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ed676bd8243856</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf8e2097b223c45</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP Senior Data Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Maple Grove, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dac275bf36488a40</t>
+          <t>https://www.indeed.com/viewjob?jk=192ac4a678cf384e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Architect-4</t>
+          <t>Databricks Engineer - Contract (contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Photon, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f5b68676765609</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e29091a2e4371e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer-6</t>
+          <t>Senior Database Developer - C13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd99fa28f8689eac</t>
+          <t>https://www.indeed.com/viewjob?jk=75576932f59b7e13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Sr. AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95a607857d8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Maple Grove, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=192ac4a678cf384e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Databricks Engineer - Contract (contract)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e29091a2e4371e</t>
+          <t>https://www.indeed.com/viewjob?jk=d01528e1099d2199</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enterprise Data- Data Engineer I</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GBU Life</t>
+          <t>Adonis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=647d32eb31b1193e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0454d0d787afaef</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Database Developer - C13</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75576932f59b7e13</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98f02f8244206</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Remote</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d567bfdb83525baa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer (SQL, AWS, &amp; Java)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
+          <t>https://www.indeed.com/viewjob?jk=93b33418deacae1b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01528e1099d2199</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb1f94893c5712e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Adonis</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0454d0d787afaef</t>
+          <t>https://www.indeed.com/viewjob?jk=e0615045d00daaed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vida Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
+          <t>IAM, RDS, GCP, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98f02f8244206</t>
+          <t>https://www.indeed.com/viewjob?jk=9f62682570ca4564</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FNBO - First National Bank of Omaha</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Scala, Data Modeling</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f82e2ce098dec35</t>
+          <t>https://www.indeed.com/viewjob?jk=a38962dce888067f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SQL, AWS, &amp; Java)</t>
+          <t>Data Engineer / Data Platform Engineer Internship Spring 2027 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b33418deacae1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fea70543399a83d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Python Developer-6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb1f94893c5712e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0b13030305a263</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0615045d00daaed</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2965ad3fac6e9b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b2194be6b7543</t>
+          <t>https://www.indeed.com/viewjob?jk=a9623715fec95146</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Engineer ADAS Fleet Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,137 +2036,137 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f62682570ca4564</t>
+          <t>https://www.indeed.com/viewjob?jk=11ad6f4a442569a8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III - Platform Application Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>A-V SERVICES INC.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38962dce888067f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9985441c9238ec</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Spring 2027 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Software Engineer – SaaS &amp; Data Migration Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Solen Software Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, Azure, GCP, Scala, SQL Server, DataOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fea70543399a83d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e93b4193751c0db</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Warehouse BI Architect Fabric</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Eatontown, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Medallion Architecture, Spark, PySpark, ETL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621931178c25b346</t>
+          <t>https://www.indeed.com/viewjob?jk=e23ac4d086e0803d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Python Developer-6</t>
+          <t>Senior Software Engineer, Reporting</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JustPark</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, GCP, BigQuery, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0b13030305a263</t>
+          <t>https://www.indeed.com/viewjob?jk=d9067ce361a1da61</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Palantir Foundry Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Kosma Tech Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2965ad3fac6e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d62cd65b081a5fd7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer ADAS Fleet Analytics</t>
+          <t>Conversational BI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Snowflake, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ad6f4a442569a8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb3b71809e4f10b7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer – SaaS &amp; Data Migration Specialist</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Solen Software Group</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, SQL Server, DataOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e93b4193751c0db</t>
+          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Conversational BI Engineer</t>
+          <t>Integration Developer/Admin (Senior Application Development Analyst)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>Judicial Council of California</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Snowflake, ELT, Power BI, MLflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, MySQL, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3b71809e4f10b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d92a3c9beacac9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
+          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Integration Developer/Admin (Senior Application Development Analyst)</t>
+          <t>Senior Full Stack .Net Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Judicial Council of California</t>
+          <t>Starr Companies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, MySQL, ETL, Talend, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d92a3c9beacac9</t>
+          <t>https://www.indeed.com/viewjob?jk=ce193f64bbb24a65</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack .Net Developer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Starr Companies</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce193f64bbb24a65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac16ebb3b7d3a45</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac16ebb3b7d3a45</t>
+          <t>https://www.indeed.com/viewjob?jk=d08c7ede9b3f07e5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08c7ede9b3f07e5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8fa8b2a51a2522</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
+          <t>BI Developer &amp; Production Support Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Snowflake, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1bbd59742c441b3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Semantic Layer &amp; Ontology Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, Dimensional Modeling, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8fa8b2a51a2522</t>
+          <t>https://www.indeed.com/viewjob?jk=327f8fe14e958d2a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer I, Data Engineering</t>
+          <t>Data Engineer-Wearables &amp; iOT Analytics (176270)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995670ae7da973ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b5d615a2b140cb52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BI Developer &amp; Production Support Engineer</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Snowflake, ELT, Power BI, MLflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1bbd59742c441b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d62003cb9f83aeb6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Semantic Layer &amp; Ontology Engineer</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, Dimensional Modeling, ELT, Power BI, MLflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327f8fe14e958d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1aa4380989d8a52</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer-Wearables &amp; iOT Analytics (176270)</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5d615a2b140cb52</t>
+          <t>https://www.indeed.com/viewjob?jk=2b84f726efca9029</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>Site Reliability Engineer- FedRamp</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62003cb9f83aeb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c05522799acac5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>Senior Site Reliability Infrastructure Engineer- Fedramp</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1aa4380989d8a52</t>
+          <t>https://www.indeed.com/viewjob?jk=08d06855bbcf79aa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>Senior Site Reliability Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b84f726efca9029</t>
+          <t>https://www.indeed.com/viewjob?jk=964c0e05d4eca96b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer- FedRamp</t>
+          <t>Apache Spark Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c05522799acac5</t>
+          <t>https://www.indeed.com/viewjob?jk=e992d6bfc308d8bb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Infrastructure Engineer- Fedramp</t>
+          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Hill's Pet Nutrition</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d06855bbcf79aa</t>
+          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (FedRAMP)</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Somerset, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, CloudWatch</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964c0e05d4eca96b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c042f7e9d0f0b75</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e992d6bfc308d8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=e2545e2fa204ae54</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hill's Pet Nutrition</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb19bd4ef6a4ada2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Somerset, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c042f7e9d0f0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=7a0f122e9187f4e1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb19bd4ef6a4ada2</t>
+          <t>https://www.indeed.com/viewjob?jk=0d07c3bb23686820</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a0f122e9187f4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=211b0a055f958ee2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d07c3bb23686820</t>
+          <t>https://www.indeed.com/viewjob?jk=64b2e71c99f69dd6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211b0a055f958ee2</t>
+          <t>https://www.indeed.com/viewjob?jk=0bdd28ae23a357c1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b2e71c99f69dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d06a6189a87b46f</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bdd28ae23a357c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc840015b470f1d</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d06a6189a87b46f</t>
+          <t>https://www.indeed.com/viewjob?jk=544fd4c8961f1ea1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc840015b470f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e32202cd85d558d0</t>
         </is>
       </c>
     </row>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544fd4c8961f1ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2c8d56a4de6d75</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Orchestration</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e32202cd85d558d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a8711133b275b7eb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2c8d56a4de6d75</t>
+          <t>https://www.indeed.com/viewjob?jk=a1054d75a23b6d7e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full Stack Engineer 4 (Global Payment Network)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8711133b275b7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb953856e305a64</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Typescript, React, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1054d75a23b6d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7b649fedb1b1f4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Global Payment Network)</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb953856e305a64</t>
+          <t>https://www.indeed.com/viewjob?jk=be3abf2400e71f03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7b649fedb1b1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f98b7445f4c23e54</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Data Platform Engineer I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3abf2400e71f03</t>
+          <t>https://www.indeed.com/viewjob?jk=c15de344a8583c9e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>AI and Software Solutions Architect (Remote, Contract)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>INFUSE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b02de3a55862c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bfa1f3245af737</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Amazon Connect Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Scala, DynamoDB, REST API integration, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98b7445f4c23e54</t>
+          <t>https://www.indeed.com/viewjob?jk=deaae074113ff24a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Platform Engineer I</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>API Gateway, RDS, Scala, Kafka, MongoDB, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15de344a8583c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c372fec6954adf93</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Amazon Connect Developer</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Scala, DynamoDB, REST API integration, Terraform</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deaae074113ff24a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>foureyes</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
+          <t>AWS, RDS, Scala, SQL Server, MySQL, MongoDB, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129e88ac4f26e5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1802ad0b463648dd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Engineering Applications</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>foureyes</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f46dbaea5d78f85</t>
+          <t>https://www.indeed.com/viewjob?jk=129e88ac4f26e5cc</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Advisor III, Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Power BI, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad035bddd06542e8</t>
+          <t>https://www.indeed.com/viewjob?jk=399a462361080234</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>First Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730949159ddc5619</t>
+          <t>https://www.indeed.com/viewjob?jk=55d0379462176349</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73326af3eb8dfe5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad035bddd06542e8</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df313ae793a47b9</t>
+          <t>https://www.indeed.com/viewjob?jk=730949159ddc5619</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Programmer I and Programmer II</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Community College of Baltimore County</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Catonsville, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70e78631b1d5b1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c73326af3eb8dfe5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Marketing Management (EMM)</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9a49c01a3e9816</t>
+          <t>https://www.indeed.com/viewjob?jk=7df313ae793a47b9</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Advisor III, Machine Learning Engineer</t>
+          <t>Programmer I and Programmer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Community College of Baltimore County</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Catonsville, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Power BI, MLOps, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399a462361080234</t>
+          <t>https://www.indeed.com/viewjob?jk=70e78631b1d5b1e5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer, Engineering Applications</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>First Bank</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87565d685b23a868</t>
+          <t>https://www.indeed.com/viewjob?jk=0f46dbaea5d78f85</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Support Engineer (TeamCity)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>First Bank</t>
+          <t>JetBrains</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,157 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19069c3d35411178</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9703405ee731b3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Wilmington, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56aea2a70012464c</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55d0379462176349</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Threat Intelligence</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Proofpoint</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, ECS, RDS, PostgreSQL, CI/CD, GitHub Actions, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3c8c0c1096d1374</t>
+          <t>https://www.indeed.com/viewjob?jk=5921dacde6ad5818</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-01.xlsx
+++ b/results/job_matches_2026-10-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Lakehouse Data Engineer- GrantSolutions experienced only</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ae16726479683f</t>
+          <t>https://www.indeed.com/viewjob?jk=16509765dca147b7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devops &amp; Data Pipeline Engineer-6</t>
+          <t>Shelton - Data Engineering - Engr- Data II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8607d279e78ca47a</t>
+          <t>https://www.indeed.com/viewjob?jk=92ef615c91382283</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Machine Learning Engineer, Predictive Maintenance</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RelMap Software</t>
+          <t>AssetWatch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,248 +587,248 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Timestream, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c20ad72a268b77</t>
+          <t>https://www.indeed.com/viewjob?jk=8a533bcbf8ae0b71</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer Consultant – BigQuery &amp; Airflow</t>
+          <t>Financial Services Technology Consulting, Financial Risk Technology (FRT) Engineering - Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Keyhole Software</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Event Hubs, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce929b1244d5c531</t>
+          <t>https://www.indeed.com/viewjob?jk=8d4e445d09c33470</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Business Intelligence Senior Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d33086583723d4</t>
+          <t>https://www.indeed.com/viewjob?jk=24dadced559e6fd5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Data Architect - Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ThinkPoint Solutions Inc</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca879c0ea096dbfb</t>
+          <t>https://www.indeed.com/viewjob?jk=8052dec6a7c72b4e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eab9d45a7707f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d212983a598443</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Promevo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab75b27388163f6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf209f051368f0a6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Devops &amp; Data Pipeline Engineer-6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9f207b6755f4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8607d279e78ca47a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pillsbury Winthrop Shaw Pittman</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4506845d5307539</t>
+          <t>https://www.indeed.com/viewjob?jk=5eab9d45a7707f9c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b97a5e70063530e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab75b27388163f6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Sr Engineer - FinOps</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e4c25ad47ec8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9f207b6755f4c7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Pillsbury Winthrop Shaw Pittman</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53e345da3563756</t>
+          <t>https://www.indeed.com/viewjob?jk=d4506845d5307539</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CMG Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Event Hubs, Kafka, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112581e70dc489f</t>
+          <t>https://www.indeed.com/viewjob?jk=b53e345da3563756</t>
         </is>
       </c>
     </row>
@@ -1028,60 +1028,60 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data (L3)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southern Hobby Distribution</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d102e066fd479ad</t>
+          <t>https://www.indeed.com/viewjob?jk=102cee0c6adcda4e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Snr. Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CIM GROUP</t>
+          <t>KnowBe4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, PostgreSQL, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, Azure, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dc346effcd7bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5cb08dca80f82f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect - Microsoft Fabric</t>
+          <t>Data Platform Engineer, Cybersecurity Operations</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc9469609f69082</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed676bd8243856</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Full Stack Developer-6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab3bff06af76c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd99fa28f8689eac</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Snr. Site Reliability Engineer (Remote)</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KnowBe4</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, Azure, GCP</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,164 +1196,164 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5cb08dca80f82f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95a607857d8a63</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer, Cybersecurity Operations</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ed676bd8243856</t>
+          <t>https://www.indeed.com/viewjob?jk=54993a3d0229e1bd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Senior Data Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FCCI Insurance Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dac275bf36488a40</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf8e2097b223c45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer-6</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Maple Grove, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd99fa28f8689eac</t>
+          <t>https://www.indeed.com/viewjob?jk=192ac4a678cf384e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Sr. Clinical Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95a607857d8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=17f0d739bf16af91</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Database Developer - C13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FCCI Insurance Group</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf8e2097b223c45</t>
+          <t>https://www.indeed.com/viewjob?jk=75576932f59b7e13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>ML Ops Engineer I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Murphy USA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maple Grove, MN, US USA</t>
+          <t>El Dorado, AR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=192ac4a678cf384e</t>
+          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Engineer - Contract (contract)</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e29091a2e4371e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbb1a0c9f6d5c59</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Database Developer - C13</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75576932f59b7e13</t>
+          <t>https://www.indeed.com/viewjob?jk=d01528e1099d2199</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Remote</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Adonis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Step Functions, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b0454d0d787afaef</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98f02f8244206</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01528e1099d2199</t>
+          <t>https://www.indeed.com/viewjob?jk=d567bfdb83525baa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Engineer (SQL, AWS, &amp; Java)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adonis</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0454d0d787afaef</t>
+          <t>https://www.indeed.com/viewjob?jk=93b33418deacae1b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SRE - DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1646,24 +1646,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98f02f8244206</t>
+          <t>https://www.indeed.com/viewjob?jk=c99c9c660d572e7c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vida Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,256 +1672,256 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, RDS, GCP, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d567bfdb83525baa</t>
+          <t>https://www.indeed.com/viewjob?jk=9f62682570ca4564</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SQL, AWS, &amp; Java)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b33418deacae1b</t>
+          <t>https://www.indeed.com/viewjob?jk=37649d4b62a2de47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Python Developer-6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb1f94893c5712e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0b13030305a263</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Site Reliability Engineer - ED&amp;A - Global Industrial</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Azure, BigQuery, Cloud Storage, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0615045d00daaed</t>
+          <t>https://www.indeed.com/viewjob?jk=e58ce9111d4e94e2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f62682570ca4564</t>
+          <t>https://www.indeed.com/viewjob?jk=a9623715fec95146</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38962dce888067f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0c66ac5431d7f0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Spring 2027 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Software Engineer III - Platform Application Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>A-V SERVICES INC.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fea70543399a83d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9985441c9238ec</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Python Developer-6</t>
+          <t>Software Engineer – SaaS &amp; Data Migration Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Solen Software Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, ECS, Azure, GCP, Scala, SQL Server, DataOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0b13030305a263</t>
+          <t>https://www.indeed.com/viewjob?jk=1e93b4193751c0db</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Warehouse BI Architect Fabric</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Eatontown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2965ad3fac6e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e23ac4d086e0803d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - ML Model Delivery</t>
+          <t>Senior Software Engineer, Reporting</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>JustPark</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, GCP, BigQuery, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9623715fec95146</t>
+          <t>https://www.indeed.com/viewjob?jk=d9067ce361a1da61</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer ADAS Fleet Analytics</t>
+          <t>Conversational BI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Snowflake, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ad6f4a442569a8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb3b71809e4f10b7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Platform Application Engineer</t>
+          <t>Palantir Foundry Full Stack Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A-V SERVICES INC.</t>
+          <t>Kosma Tech Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9985441c9238ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d62cd65b081a5fd7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer – SaaS &amp; Data Migration Specialist</t>
+          <t>Integration Developer/Admin (Senior Application Development Analyst)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Solen Software Group</t>
+          <t>Judicial Council of California</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, SQL Server, DataOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, MySQL, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e93b4193751c0db</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d92a3c9beacac9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Warehouse BI Architect Fabric</t>
+          <t>Senior Full Stack .Net Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Starr Companies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eatontown, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23ac4d086e0803d</t>
+          <t>https://www.indeed.com/viewjob?jk=ce193f64bbb24a65</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Reporting</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JustPark</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, GCP, BigQuery, Data Modeling, ELT, dbt</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9067ce361a1da61</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac16ebb3b7d3a45</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Palantir Foundry Full Stack Developer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kosma Tech Inc</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,182 +2201,182 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62cd65b081a5fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=d08c7ede9b3f07e5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Conversational BI Engineer</t>
+          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Snowflake, ELT, Power BI, MLflow</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3b71809e4f10b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Analytics Data Engineer II - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
+          <t>https://www.indeed.com/viewjob?jk=196fad23ac814fb2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Integration Developer/Admin (Senior Application Development Analyst)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Judicial Council of California</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, MySQL, ETL, Talend, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d92a3c9beacac9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8fa8b2a51a2522</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
+          <t>Senior Analytics Engineer (Data Platform &amp; AI Enablement)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
+          <t>https://www.indeed.com/viewjob?jk=c028808e0e50f38b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack .Net Developer</t>
+          <t>BI Developer &amp; Production Support Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Starr Companies</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Snowflake, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce193f64bbb24a65</t>
+          <t>https://www.indeed.com/viewjob?jk=f1bbd59742c441b3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Enterprise Semantic Layer &amp; Ontology Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, Dimensional Modeling, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac16ebb3b7d3a45</t>
+          <t>https://www.indeed.com/viewjob?jk=327f8fe14e958d2a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Dataflow, Data Modeling, Splunk, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08c7ede9b3f07e5</t>
+          <t>https://www.indeed.com/viewjob?jk=35a87a481b03a8f0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Somerset, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8fa8b2a51a2522</t>
+          <t>https://www.indeed.com/viewjob?jk=1c042f7e9d0f0b75</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BI Developer &amp; Production Support Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Snowflake, ELT, Power BI, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1bbd59742c441b3</t>
+          <t>https://www.indeed.com/viewjob?jk=35397f2df8eceb18</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Semantic Layer &amp; Ontology Engineer</t>
+          <t>Agile Product Management Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sapta Global</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, Dimensional Modeling, ELT, Power BI, MLflow</t>
+          <t>AWS, Hadoop, Kafka, Oracle, MongoDB, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327f8fe14e958d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=e927f38fa21e4ff6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer-Wearables &amp; iOT Analytics (176270)</t>
+          <t>Agile Product Management Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
+          <t>AWS, Hadoop, Kafka, Oracle, MongoDB, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5d615a2b140cb52</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcc063ff491fc81</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Department of Motor Vehicles California</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62003cb9f83aeb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd56cb6c6641f35</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>Full Stack Engineer 4 (Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1aa4380989d8a52</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa0a61b0b1456bb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b84f726efca9029</t>
+          <t>https://www.indeed.com/viewjob?jk=3c87481ab8ef4260</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer- FedRamp</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c05522799acac5</t>
+          <t>https://www.indeed.com/viewjob?jk=e2545e2fa204ae54</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Infrastructure Engineer- Fedramp</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d06855bbcf79aa</t>
+          <t>https://www.indeed.com/viewjob?jk=fb19bd4ef6a4ada2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (FedRAMP)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964c0e05d4eca96b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a0f122e9187f4e1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e992d6bfc308d8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=0d07c3bb23686820</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hill's Pet Nutrition</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=211b0a055f958ee2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Full-Stack Engineer 5</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Somerset, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c042f7e9d0f0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=64b2e71c99f69dd6</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545e2fa204ae54</t>
+          <t>https://www.indeed.com/viewjob?jk=0bdd28ae23a357c1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb19bd4ef6a4ada2</t>
+          <t>https://www.indeed.com/viewjob?jk=2d06a6189a87b46f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a0f122e9187f4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc840015b470f1d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d07c3bb23686820</t>
+          <t>https://www.indeed.com/viewjob?jk=544fd4c8961f1ea1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211b0a055f958ee2</t>
+          <t>https://www.indeed.com/viewjob?jk=e32202cd85d558d0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b2e71c99f69dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2c8d56a4de6d75</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bdd28ae23a357c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a8711133b275b7eb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d06a6189a87b46f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1054d75a23b6d7e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full Stack Engineer 4 (Global Payment Network)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc840015b470f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb953856e305a64</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544fd4c8961f1ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7b649fedb1b1f4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Orchestration</t>
+          <t>Junior Azure Data Engineer - UniFirst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e32202cd85d558d0</t>
+          <t>https://www.indeed.com/viewjob?jk=24ec3bf6a35a904c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2c8d56a4de6d75</t>
+          <t>https://www.indeed.com/viewjob?jk=be3abf2400e71f03</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8711133b275b7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=620b02de3a55862c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Typescript, React, AWS)</t>
+          <t>Data Engineer – Azure</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Symphony Enterprises Llc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1054d75a23b6d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b8c1c6cf55d819e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Global Payment Network)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,59 +3436,59 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb953856e305a64</t>
+          <t>https://www.indeed.com/viewjob?jk=f98b7445f4c23e54</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Platform Engineer I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7b649fedb1b1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c15de344a8583c9e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>AI and Software Solutions Architect (Remote, Contract)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>INFUSE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3abf2400e71f03</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bfa1f3245af737</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>API Gateway, RDS, Scala, Kafka, MongoDB, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98b7445f4c23e54</t>
+          <t>https://www.indeed.com/viewjob?jk=c372fec6954adf93</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Platform Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Athena, Step Functions, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15de344a8583c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=baa8123cd97b3b0d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI and Software Solutions Architect (Remote, Contract)</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>INFUSE</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bfa1f3245af737</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Amazon Connect Developer</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Scala, DynamoDB, REST API integration, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deaae074113ff24a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad035bddd06542e8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Scala, Kafka, MongoDB, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c372fec6954adf93</t>
+          <t>https://www.indeed.com/viewjob?jk=730949159ddc5619</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
+          <t>https://www.indeed.com/viewjob?jk=c73326af3eb8dfe5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, MySQL, MongoDB, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1802ad0b463648dd</t>
+          <t>https://www.indeed.com/viewjob?jk=7df313ae793a47b9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Software Engineer, Engineering Applications</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>foureyes</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129e88ac4f26e5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f46dbaea5d78f85</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI and Software Solutions Architect (Remote, Contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>INFUSE</t>
+          <t>First Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfbdeb14e9a28d7</t>
+          <t>https://www.indeed.com/viewjob?jk=55d0379462176349</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Advisor III, Machine Learning Engineer</t>
+          <t>Engineer IV, ECM Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,297 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Power BI, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399a462361080234</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55d0379462176349</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer, Marketing</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>IMG Academy</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad035bddd06542e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer, Marketing</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>NCSA College Recruiting</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=730949159ddc5619</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer, Marketing</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>IMG Academy</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c73326af3eb8dfe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer, Marketing</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>NCSA College Recruiting</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7df313ae793a47b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Programmer I and Programmer II</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Community College of Baltimore County</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Catonsville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70e78631b1d5b1e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Engineering Applications</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f46dbaea5d78f85</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Support Engineer (TeamCity)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>JetBrains</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5921dacde6ad5818</t>
+          <t>https://www.indeed.com/viewjob?jk=992ec04c34232f03</t>
         </is>
       </c>
     </row>
